--- a/Test Cases/Login_Test_Cases.xlsx
+++ b/Test Cases/Login_Test_Cases.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Login Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,23 +25,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -55,17 +90,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -428,1174 +468,1204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TC ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TICHI WEB APPLICATION - LOGIN TEST CASES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="29" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Tichi Web Application</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="29" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Document Name</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Login Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Application URL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>https://tichi-app-webapp-stage.web.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="43.5" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Prepared By</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Sudharsan D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="43.5" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="29" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Test Case Name</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Test Type</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="29" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LOGIN_001</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Verify Login page loads successfully</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Application URL available</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Open application URL</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Login page displayed</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Verify Email field is displayed</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Application is accessible</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Open URL
+2. Observe Login page</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Login page should load with all controls</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Login page loaded successfully with email, Google Sign-In and Continue button.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="29" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LOGIN_002</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Verify Google Sign-In option is displayed</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Login page opened</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Observe Email field</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Email field displayed</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Verify Continue button is displayed</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Login page opened</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Observe Continue button</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Continue button displayed</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Verify Email field is mandatory</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Login page opened</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Leave Email blank and click Continue</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Blank</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Validation displayed</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Verify invalid email format validation</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Login page opened</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Enter invalid email</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Invalid email format</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Validation displayed</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Verify valid email navigates to password page</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Registered account</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Enter valid email and Continue</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Login page</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Google Sign-In option should be visible</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Google Sign-In option is displayed.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="29" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LOGIN_003</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Verify Continue button with valid email</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Valid registered email</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Password page displayed</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Verify Password field is displayed</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Password page</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Observe Password field</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Password field displayed</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Verify Password field is mandatory</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Password page</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Leave Password blank</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Blank</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Validation displayed</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Verify successful login</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Verified account</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Enter valid credentials</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Valid registered email &amp; valid password</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>User logged in</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOGIN_010</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Verify login with invalid password</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Verified account</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Enter invalid password</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Valid email &amp; invalid password</t>
+          <t>1.Enter valid email
+2.Click Continue</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Invalid login details</t>
+          <t>Navigate to password page</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
+          <t>Password page displayed.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_011</t>
+          <t>LOGIN_004</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify password page displays selected email</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Verify login with non-existing (unregistered) email</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Login page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Enter a non-existing email address and click Continue/Login</t>
+          <t>Reached password page</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>nonexisting@test.com</t>
+          <t>1.Verify email field</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System displays 'Invalid login details' or 'User not found' and remains on Login page</t>
+          <t>Entered email should persist</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t>Email retained on password page.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_012</t>
+          <t>LOGIN_005</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify successful login</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Verify password visibility toggle</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Password entered</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Click eye icon</t>
+          <t>Valid credentials</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Valid password</t>
+          <t>1.Enter valid email
+2.Enter valid password
+3.Click Login</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Password visibility toggles</t>
+          <t>User should reach dashboard</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
+          <t>User was successfully authenticated and redirected to the dashboard.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="29" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_013</t>
+          <t>LOGIN_006</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify login with invalid password</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Verify Forgot Password navigation</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Password page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Click Forgot Password</t>
+          <t>Registered email</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.Enter valid email
+2.Enter invalid password
+3.Click Login</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password page opens</t>
+          <t>Authentication should fail with generic error</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+          <t>Application displayed 'Invalid login details'.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Validation displayed correctly.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_014</t>
+          <t>LOGIN_007</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify login with unregistered email</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Verify password reset with registered email</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Submit registered email</t>
+          <t>Unregistered email</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Registered email</t>
+          <t>1.Enter unregistered email
+2.Continue</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Verification email sent</t>
+          <t>The application should redirect the user to the Sign Up page when an unregistered email address is entered.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+          <t>The application redirected the user to the Sign Up page after entering an unregistered email address.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Application redirected the user to the registration flow as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_015</t>
+          <t>LOGIN_008</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify empty email</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Verify password reset with unregistered email</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Submit unregistered email</t>
+          <t>Login page</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Unregistered email</t>
+          <t>1.Leave email blank
+2.Click Continue</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Proper error displayed</t>
+          <t>Required validation should appear</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
+          <t>Application displayed 'Email is required'.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="29" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_016</t>
+          <t>LOGIN_009</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify invalid email format</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Verify Google Sign-In</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Login page</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Click Continue with Google</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Valid Google account</t>
+          <t>1.Enter invalid email
+2.Click Continue</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Google auth opens</t>
+          <t>System/browser should validate email format</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+          <t>Browser displayed '@' missing validation.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Validation displayed correctly.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_017</t>
+          <t>LOGIN_010</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify empty password</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Verify login using Enter key</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Credentials entered</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Press Enter</t>
+          <t>Password page</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Valid credentials</t>
+          <t>1.Leave password blank
+2.Click Login</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>Required validation should appear</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t>Displayed 'Password is required'.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Validation displayed correctly.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_018</t>
+          <t>LOGIN_011</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify password visibility toggle</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Verify email with leading spaces</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Login page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Enter email with leading spaces</t>
+          <t>Password page</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Email with leading spaces</t>
+          <t>1.Click eye icon</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Spaces handled</t>
+          <t>Password visibility should toggle</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Password toggled </t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_019</t>
+          <t>LOGIN_012</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify Forgot Password link</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Verify email with trailing spaces</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Login page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Enter email with trailing spaces</t>
+          <t>Password page</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Email with trailing spaces</t>
+          <t>1.Click Forgot Password</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Spaces handled</t>
+          <t>Forgot Password page should open</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
+          <t>Forgot Password page opened.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="43.5" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_020</t>
+          <t>LOGIN_013</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify reset password request</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Verify SQL injection protection</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Login page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Enter SQL payload</t>
+          <t>Forgot Password page</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>SQL payload</t>
+          <t>1.Enter email
+2.Click Send Verification</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Authentication not bypassed</t>
+          <t>Confirmation should be displayed</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>'Check your Email' confirmation displayed.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_021</t>
+          <t>LOGIN_014</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify Back navigation from Forgot Password</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Verify XSS protection</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Login page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Enter script payload</t>
+          <t>Forgot Password page</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>XSS payload</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Script not executed</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+          <t>1.Click Back</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>The application should navigate back to the Login page.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>The application successfully navigated back to Login page.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Back navigation is working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_022</t>
+          <t>LOGIN_015</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify Continue button disabled/enabled behavior</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple login attempts</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>Login page</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Attempt invalid login repeatedly</t>
-        </is>
-      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Invalid credentials</t>
+          <t>1.Enter valid email</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Application handles attempts</t>
+          <t>Continue should proceed only with valid input</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t>Valid email proceeded to password page.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_023</t>
+          <t>LOGIN_016</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify mandatory Email field</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Verify page refresh</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>Login page</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Refresh browser</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.Do not enter email</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Page reloads correctly</t>
+          <t>System should display a mandatory field validation message and prevent the user from proceeding.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+          <t>The application displayed the required field validation message and prevented navigation to the password page.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Required field validation displayed correctly.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_024</t>
+          <t>LOGIN_017</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify Login button presence</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Verify keyboard tab navigation</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Login page</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Use Tab key</t>
+          <t>Password page</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>1.Open password page</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Correct focus order</t>
+          <t>Login button should be visible</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t>Login button displayed.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC_LOGIN_025</t>
+          <t>LOGIN_018</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Verify error message security</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Verify responsive UI</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Resize browser</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Observe layout</t>
+          <t>Invalid credentials</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Desktop/Mobile</t>
+          <t>1.Login with wrong password</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>UI aligned</t>
+          <t>Generic error without exposing sensitive info</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+          <t>Displayed generic 'Invalid login details'.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Security-friendly message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LOGIN_019</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Verify email remains editable</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Password page</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1.Click Edit</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Email should be editable</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Edit option displayed.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LOGIN_020</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI elements render correctly</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Application accessible</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1.Open login flow</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>All UI elements, including labels, input fields, buttons, and links, should be properly aligned and displayed without layout or formatting issues.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>All UI elements were properly aligned and rendered correctly. No layout or formatting issues were observed during testing.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>UI layout verified successfully. No visual defects identified.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>